--- a/Excel/Summary_Report.xlsx
+++ b/Excel/Summary_Report.xlsx
@@ -444,7 +444,7 @@
         <v>Duration</v>
       </c>
       <c r="B6" t="str">
-        <v>1.15s</v>
+        <v>1.32s</v>
       </c>
     </row>
   </sheetData>
